--- a/Jobs/Tasks/FileProcess/TempFile_Zone.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile_Zone.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishal Khedkar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HMS2\Jobs\Tasks\FileProcess\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1375,7 +1375,7 @@
     <col min="131" max="131" width="19" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="14" bestFit="1" customWidth="1"/>
     <col min="133" max="133" width="16" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="14.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="10.54296875" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:134" x14ac:dyDescent="0.35">

--- a/Jobs/Tasks/FileProcess/TempFile_Zone.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile_Zone.xlsx
@@ -828,7 +828,7 @@
     <t>South</t>
   </si>
   <si>
-    <t>AG26020300001</t>
+    <t>AG2602191401001</t>
   </si>
 </sst>
 </file>
